--- a/technology_surveys/015_web_services_expertise_survey--technology_surveys.xlsx
+++ b/technology_surveys/015_web_services_expertise_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -814,29 +814,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>graphql</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GraphQL</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>experience_with_apis_choices</t>
+          <t>expertise_in_web_services_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
@@ -848,12 +848,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -882,29 +882,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>expertise_in_web_services_choices</t>
+          <t>current_usage_of_web_services_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>internal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>Internal</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>external</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>cloud</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Cloud</t>
         </is>
       </c>
     </row>
@@ -950,29 +950,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cloud</t>
+          <t>on-premises</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cloud</t>
+          <t>On-premises</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_usage_of_web_services_choices</t>
+          <t>proficiency_in_apis_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>on-premises</t>
+          <t>rest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>On-premises</t>
+          <t>REST</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rest</t>
+          <t>graphql</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>GraphQL</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>graphql</t>
+          <t>soap</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GraphQL</t>
+          <t>SOAP</t>
         </is>
       </c>
     </row>
@@ -1018,29 +1018,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>soap</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOAP</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proficiency_in_apis_choices</t>
+          <t>tools_used_for_web_services_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>postman</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Postman</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>postman</t>
+          <t>curl</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Postman</t>
+          <t>cURL</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>curl</t>
+          <t>soapui</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cURL</t>
+          <t>SoapUI</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>soapui</t>
+          <t>postman/soapui</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SoapUI</t>
+          <t>Postman/SoapUI</t>
         </is>
       </c>
     </row>
@@ -1103,29 +1103,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>postman/soapui</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Postman/SoapUI</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tools_used_for_web_services_choices</t>
+          <t>web_services_experience_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>other_(please_specify)</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Other (please specify)</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>less_than_1_year</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Less than 1 year</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1-2_years</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2-5_years</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2-5 years</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5-10_years</t>
+          <t>more_than_10_years</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>5-10 years</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>web_services_experience_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>more_than_10_years</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>More than 10 years</t>
         </is>
